--- a/dados/administrativos.xlsx
+++ b/dados/administrativos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30516"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30524"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4C9AD3EB-E3DA-4217-8903-BE9E590E2DCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B6B90ED7-DB57-4272-B5D0-1C3C77D4EDD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="60">
   <si>
     <t>Id</t>
   </si>
@@ -192,6 +192,30 @@
   </si>
   <si>
     <t xml:space="preserve">Sem sugestões </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoramento nas guarita principalmente </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoramento na guaritas </t>
+  </si>
+  <si>
+    <t>Ok</t>
+  </si>
+  <si>
+    <t>nada a comentar para melhorias</t>
+  </si>
+  <si>
+    <t>A empresa já desenvolve diversas iniciativas importantes para os colaboradores. Como sugestão de melhoria, acredito que podemos avançar cada vez mais na integração entre as áreas, na simplificação de processos e no acompanhamento das sugestões apresentadas pela equipe, buscando tornar o dia a dia ainda mais eficiente e colaborativo.</t>
+  </si>
+  <si>
+    <t>...</t>
+  </si>
+  <si>
+    <t>Mtu bom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devido a segurança não tem proteção própria </t>
   </si>
 </sst>
 </file>
@@ -298,8 +322,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:R29" totalsRowShown="0">
-  <autoFilter ref="A1:R29" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:R37" totalsRowShown="0">
+  <autoFilter ref="A1:R37" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="18">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="15">
       <extLst>
@@ -431,7 +455,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="rt8JIBHfx0mATf2o1c2YZSr5bAZAsa1Hi1pL7TTHnqJUODZHUjNKOElGSE80SEwyMlBDUE1GN0dPMS4u" isFormConnected="1" maxResponseId="28" latestEventMarker="0">
+      <xlmsforms:msForm id="rt8JIBHfx0mATf2o1c2YZSr5bAZAsa1Hi1pL7TTHnqJUODZHUjNKOElGSE80SEwyMlBDUE1GN0dPMS4u" isFormConnected="1" maxResponseId="36" latestEventMarker="8">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -753,7 +777,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R29"/>
+  <dimension ref="A1:R37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="18" width="20" bestFit="1" customWidth="1"/>
@@ -2299,6 +2323,430 @@
         <v>51</v>
       </c>
     </row>
+    <row r="30" spans="1:18">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2">
+        <v>46293.41201388889</v>
+      </c>
+      <c r="C30" s="2">
+        <v>46293.415208333332</v>
+      </c>
+      <c r="D30" t="s">
+        <v>18</v>
+      </c>
+      <c r="F30" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" t="s">
+        <v>19</v>
+      </c>
+      <c r="H30" t="s">
+        <v>19</v>
+      </c>
+      <c r="I30" t="s">
+        <v>19</v>
+      </c>
+      <c r="J30" t="s">
+        <v>19</v>
+      </c>
+      <c r="K30" t="s">
+        <v>19</v>
+      </c>
+      <c r="L30" t="s">
+        <v>19</v>
+      </c>
+      <c r="M30" t="s">
+        <v>19</v>
+      </c>
+      <c r="N30" t="s">
+        <v>19</v>
+      </c>
+      <c r="O30" t="s">
+        <v>20</v>
+      </c>
+      <c r="P30" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>19</v>
+      </c>
+      <c r="R30" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2">
+        <v>46293.411886574075</v>
+      </c>
+      <c r="C31" s="2">
+        <v>46293.416527777779</v>
+      </c>
+      <c r="D31" t="s">
+        <v>18</v>
+      </c>
+      <c r="F31" t="s">
+        <v>21</v>
+      </c>
+      <c r="G31" t="s">
+        <v>21</v>
+      </c>
+      <c r="H31" t="s">
+        <v>21</v>
+      </c>
+      <c r="I31" t="s">
+        <v>21</v>
+      </c>
+      <c r="J31" t="s">
+        <v>21</v>
+      </c>
+      <c r="K31" t="s">
+        <v>19</v>
+      </c>
+      <c r="L31" t="s">
+        <v>21</v>
+      </c>
+      <c r="M31" t="s">
+        <v>21</v>
+      </c>
+      <c r="N31" t="s">
+        <v>21</v>
+      </c>
+      <c r="O31" t="s">
+        <v>21</v>
+      </c>
+      <c r="P31" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>19</v>
+      </c>
+      <c r="R31" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2">
+        <v>46293.440439814818</v>
+      </c>
+      <c r="C32" s="2">
+        <v>46293.440821759257</v>
+      </c>
+      <c r="D32" t="s">
+        <v>18</v>
+      </c>
+      <c r="F32" t="s">
+        <v>21</v>
+      </c>
+      <c r="G32" t="s">
+        <v>21</v>
+      </c>
+      <c r="H32" t="s">
+        <v>21</v>
+      </c>
+      <c r="I32" t="s">
+        <v>20</v>
+      </c>
+      <c r="J32" t="s">
+        <v>21</v>
+      </c>
+      <c r="K32" t="s">
+        <v>21</v>
+      </c>
+      <c r="L32" t="s">
+        <v>21</v>
+      </c>
+      <c r="M32" t="s">
+        <v>21</v>
+      </c>
+      <c r="N32" t="s">
+        <v>21</v>
+      </c>
+      <c r="O32" t="s">
+        <v>21</v>
+      </c>
+      <c r="P32" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>22</v>
+      </c>
+      <c r="R32" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2">
+        <v>46293.440763888888</v>
+      </c>
+      <c r="C33" s="2">
+        <v>46293.442337962966</v>
+      </c>
+      <c r="D33" t="s">
+        <v>18</v>
+      </c>
+      <c r="F33" t="s">
+        <v>21</v>
+      </c>
+      <c r="G33" t="s">
+        <v>21</v>
+      </c>
+      <c r="H33" t="s">
+        <v>21</v>
+      </c>
+      <c r="I33" t="s">
+        <v>21</v>
+      </c>
+      <c r="J33" t="s">
+        <v>21</v>
+      </c>
+      <c r="K33" t="s">
+        <v>21</v>
+      </c>
+      <c r="L33" t="s">
+        <v>20</v>
+      </c>
+      <c r="M33" t="s">
+        <v>20</v>
+      </c>
+      <c r="N33" t="s">
+        <v>19</v>
+      </c>
+      <c r="O33" t="s">
+        <v>20</v>
+      </c>
+      <c r="P33" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>21</v>
+      </c>
+      <c r="R33" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2">
+        <v>46293.483946759261</v>
+      </c>
+      <c r="C34" s="2">
+        <v>46293.48609953704</v>
+      </c>
+      <c r="D34" t="s">
+        <v>18</v>
+      </c>
+      <c r="F34" t="s">
+        <v>19</v>
+      </c>
+      <c r="G34" t="s">
+        <v>21</v>
+      </c>
+      <c r="H34" t="s">
+        <v>19</v>
+      </c>
+      <c r="I34" t="s">
+        <v>19</v>
+      </c>
+      <c r="J34" t="s">
+        <v>19</v>
+      </c>
+      <c r="K34" t="s">
+        <v>21</v>
+      </c>
+      <c r="L34" t="s">
+        <v>19</v>
+      </c>
+      <c r="M34" t="s">
+        <v>19</v>
+      </c>
+      <c r="N34" t="s">
+        <v>19</v>
+      </c>
+      <c r="O34" t="s">
+        <v>21</v>
+      </c>
+      <c r="P34" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>21</v>
+      </c>
+      <c r="R34" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2">
+        <v>46293.555266203701</v>
+      </c>
+      <c r="C35" s="2">
+        <v>46293.556284722225</v>
+      </c>
+      <c r="D35" t="s">
+        <v>18</v>
+      </c>
+      <c r="F35" t="s">
+        <v>21</v>
+      </c>
+      <c r="G35" t="s">
+        <v>20</v>
+      </c>
+      <c r="H35" t="s">
+        <v>20</v>
+      </c>
+      <c r="I35" t="s">
+        <v>20</v>
+      </c>
+      <c r="J35" t="s">
+        <v>19</v>
+      </c>
+      <c r="K35" t="s">
+        <v>19</v>
+      </c>
+      <c r="L35" t="s">
+        <v>22</v>
+      </c>
+      <c r="M35" t="s">
+        <v>21</v>
+      </c>
+      <c r="N35" t="s">
+        <v>19</v>
+      </c>
+      <c r="O35" t="s">
+        <v>20</v>
+      </c>
+      <c r="P35" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>21</v>
+      </c>
+      <c r="R35" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2">
+        <v>46293.567442129628</v>
+      </c>
+      <c r="C36" s="2">
+        <v>46293.569039351853</v>
+      </c>
+      <c r="D36" t="s">
+        <v>18</v>
+      </c>
+      <c r="F36" t="s">
+        <v>21</v>
+      </c>
+      <c r="G36" t="s">
+        <v>21</v>
+      </c>
+      <c r="H36" t="s">
+        <v>21</v>
+      </c>
+      <c r="I36" t="s">
+        <v>21</v>
+      </c>
+      <c r="J36" t="s">
+        <v>21</v>
+      </c>
+      <c r="K36" t="s">
+        <v>21</v>
+      </c>
+      <c r="L36" t="s">
+        <v>21</v>
+      </c>
+      <c r="M36" t="s">
+        <v>21</v>
+      </c>
+      <c r="N36" t="s">
+        <v>21</v>
+      </c>
+      <c r="O36" t="s">
+        <v>21</v>
+      </c>
+      <c r="P36" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>21</v>
+      </c>
+      <c r="R36" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2">
+        <v>46293.585034722222</v>
+      </c>
+      <c r="C37" s="2">
+        <v>46293.589525462965</v>
+      </c>
+      <c r="D37" t="s">
+        <v>18</v>
+      </c>
+      <c r="F37" t="s">
+        <v>19</v>
+      </c>
+      <c r="G37" t="s">
+        <v>21</v>
+      </c>
+      <c r="H37" t="s">
+        <v>19</v>
+      </c>
+      <c r="I37" t="s">
+        <v>19</v>
+      </c>
+      <c r="J37" t="s">
+        <v>19</v>
+      </c>
+      <c r="K37" t="s">
+        <v>31</v>
+      </c>
+      <c r="L37" t="s">
+        <v>21</v>
+      </c>
+      <c r="M37" t="s">
+        <v>21</v>
+      </c>
+      <c r="N37" t="s">
+        <v>19</v>
+      </c>
+      <c r="O37" t="s">
+        <v>19</v>
+      </c>
+      <c r="P37" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>20</v>
+      </c>
+      <c r="R37" t="s">
+        <v>59</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/dados/administrativos.xlsx
+++ b/dados/administrativos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B6B90ED7-DB57-4272-B5D0-1C3C77D4EDD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{70789BCF-1882-4E39-8283-4C9C1BEDC15B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="65">
   <si>
     <t>Id</t>
   </si>
@@ -216,6 +216,21 @@
   </si>
   <si>
     <t xml:space="preserve">Devido a segurança não tem proteção própria </t>
+  </si>
+  <si>
+    <t>Deveria olha mais um pouco na segurança externa e interna</t>
+  </si>
+  <si>
+    <t>A lanchonete do campus dois continua a não aceitar o voucher, o que é inadmissível.</t>
+  </si>
+  <si>
+    <t>Preço dos itens  da lanchonete sao extremamente superfaturados, sinal de WiFi em certas partes do campus nao funciona ou o sinal e fraco, estrutura de ambiente de descanso para colaboradores deve ser tratado com carinho principalmente na Escola Fazenda onde NÃO existe esse espaço.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ta bom mais precisa melhorar tipo ter uma sala de convivência para os funcionários almoçarem </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compartilhar as informações necessárias em tempo  hábil. </t>
   </si>
 </sst>
 </file>
@@ -322,8 +337,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:R37" totalsRowShown="0">
-  <autoFilter ref="A1:R37" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:R42" totalsRowShown="0">
+  <autoFilter ref="A1:R42" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="18">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="15">
       <extLst>
@@ -455,7 +470,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="rt8JIBHfx0mATf2o1c2YZSr5bAZAsa1Hi1pL7TTHnqJUODZHUjNKOElGSE80SEwyMlBDUE1GN0dPMS4u" isFormConnected="1" maxResponseId="36" latestEventMarker="8">
+      <xlmsforms:msForm id="rt8JIBHfx0mATf2o1c2YZSr5bAZAsa1Hi1pL7TTHnqJUODZHUjNKOElGSE80SEwyMlBDUE1GN0dPMS4u" isFormConnected="1" maxResponseId="41" latestEventMarker="13">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -777,7 +792,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R37"/>
+  <dimension ref="A1:R42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="18" width="20" bestFit="1" customWidth="1"/>
@@ -2747,6 +2762,271 @@
         <v>59</v>
       </c>
     </row>
+    <row r="38" spans="1:18">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2">
+        <v>46293.863425925927</v>
+      </c>
+      <c r="C38" s="2">
+        <v>46293.865543981483</v>
+      </c>
+      <c r="D38" t="s">
+        <v>18</v>
+      </c>
+      <c r="F38" t="s">
+        <v>21</v>
+      </c>
+      <c r="G38" t="s">
+        <v>21</v>
+      </c>
+      <c r="H38" t="s">
+        <v>19</v>
+      </c>
+      <c r="I38" t="s">
+        <v>19</v>
+      </c>
+      <c r="J38" t="s">
+        <v>19</v>
+      </c>
+      <c r="K38" t="s">
+        <v>19</v>
+      </c>
+      <c r="L38" t="s">
+        <v>20</v>
+      </c>
+      <c r="M38" t="s">
+        <v>19</v>
+      </c>
+      <c r="N38" t="s">
+        <v>19</v>
+      </c>
+      <c r="O38" t="s">
+        <v>21</v>
+      </c>
+      <c r="P38" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>20</v>
+      </c>
+      <c r="R38" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2">
+        <v>46293.880856481483</v>
+      </c>
+      <c r="C39" s="2">
+        <v>46293.881851851853</v>
+      </c>
+      <c r="D39" t="s">
+        <v>18</v>
+      </c>
+      <c r="F39" t="s">
+        <v>19</v>
+      </c>
+      <c r="G39" t="s">
+        <v>19</v>
+      </c>
+      <c r="H39" t="s">
+        <v>19</v>
+      </c>
+      <c r="I39" t="s">
+        <v>19</v>
+      </c>
+      <c r="J39" t="s">
+        <v>21</v>
+      </c>
+      <c r="K39" t="s">
+        <v>21</v>
+      </c>
+      <c r="L39" t="s">
+        <v>19</v>
+      </c>
+      <c r="M39" t="s">
+        <v>21</v>
+      </c>
+      <c r="N39" t="s">
+        <v>21</v>
+      </c>
+      <c r="O39" t="s">
+        <v>20</v>
+      </c>
+      <c r="P39" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>19</v>
+      </c>
+      <c r="R39" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2">
+        <v>46294.069641203707</v>
+      </c>
+      <c r="C40" s="2">
+        <v>46294.078275462962</v>
+      </c>
+      <c r="D40" t="s">
+        <v>18</v>
+      </c>
+      <c r="F40" t="s">
+        <v>21</v>
+      </c>
+      <c r="G40" t="s">
+        <v>20</v>
+      </c>
+      <c r="H40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I40" t="s">
+        <v>20</v>
+      </c>
+      <c r="J40" t="s">
+        <v>22</v>
+      </c>
+      <c r="K40" t="s">
+        <v>31</v>
+      </c>
+      <c r="L40" t="s">
+        <v>20</v>
+      </c>
+      <c r="M40" t="s">
+        <v>21</v>
+      </c>
+      <c r="N40" t="s">
+        <v>19</v>
+      </c>
+      <c r="O40" t="s">
+        <v>22</v>
+      </c>
+      <c r="P40" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>19</v>
+      </c>
+      <c r="R40" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" s="2">
+        <v>46294.587395833332</v>
+      </c>
+      <c r="C41" s="2">
+        <v>46294.588773148149</v>
+      </c>
+      <c r="D41" t="s">
+        <v>18</v>
+      </c>
+      <c r="F41" t="s">
+        <v>21</v>
+      </c>
+      <c r="G41" t="s">
+        <v>21</v>
+      </c>
+      <c r="H41" t="s">
+        <v>21</v>
+      </c>
+      <c r="I41" t="s">
+        <v>20</v>
+      </c>
+      <c r="J41" t="s">
+        <v>21</v>
+      </c>
+      <c r="K41" t="s">
+        <v>22</v>
+      </c>
+      <c r="L41" t="s">
+        <v>21</v>
+      </c>
+      <c r="M41" t="s">
+        <v>21</v>
+      </c>
+      <c r="N41" t="s">
+        <v>21</v>
+      </c>
+      <c r="O41" t="s">
+        <v>21</v>
+      </c>
+      <c r="P41" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>20</v>
+      </c>
+      <c r="R41" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2">
+        <v>46294.672256944446</v>
+      </c>
+      <c r="C42" s="2">
+        <v>46294.672719907408</v>
+      </c>
+      <c r="D42" t="s">
+        <v>18</v>
+      </c>
+      <c r="F42" t="s">
+        <v>19</v>
+      </c>
+      <c r="G42" t="s">
+        <v>19</v>
+      </c>
+      <c r="H42" t="s">
+        <v>19</v>
+      </c>
+      <c r="I42" t="s">
+        <v>21</v>
+      </c>
+      <c r="J42" t="s">
+        <v>19</v>
+      </c>
+      <c r="K42" t="s">
+        <v>19</v>
+      </c>
+      <c r="L42" t="s">
+        <v>19</v>
+      </c>
+      <c r="M42" t="s">
+        <v>19</v>
+      </c>
+      <c r="N42" t="s">
+        <v>19</v>
+      </c>
+      <c r="O42" t="s">
+        <v>20</v>
+      </c>
+      <c r="P42" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>19</v>
+      </c>
+      <c r="R42" t="s">
+        <v>64</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/dados/administrativos.xlsx
+++ b/dados/administrativos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30524"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{70789BCF-1882-4E39-8283-4C9C1BEDC15B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{416327C5-A3DF-40C7-AA74-71B3A97775A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="802" uniqueCount="78">
   <si>
     <t>Id</t>
   </si>
@@ -231,6 +231,45 @@
   </si>
   <si>
     <t xml:space="preserve">Compartilhar as informações necessárias em tempo  hábil. </t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ótimo </t>
+  </si>
+  <si>
+    <t>sem declarações , tudo ótimo !!</t>
+  </si>
+  <si>
+    <t>não há</t>
+  </si>
+  <si>
+    <t>Sugere-se a melhoria na qualidade dos alimentos oferecidos pela lanchonete, buscando maior variedade, qualidade e padronização dos produtos disponibilizados aos colaboradores e usuários.  Também seria importante a padronização e divulgação dos preços dos produtos, com a disponibilização de um cardápio ou tabela de preços em local visível. Atualmente, os valores não estão fixados ou expostos, fazendo com que cada funcionário informe um preço diferente, o que pode gerar dúvidas e falta de padronização nas informações.  A exposição clara dos produtos e respectivos preços contribuiria para maior transparência, organização, praticidade e segurança para os consumidores, além de proporcionar um atendimento mais uniforme.</t>
+  </si>
+  <si>
+    <t>Como sugestão de melhoria, acredito que a comunicação interna poderia ser mais clara, ágil e alinhada entre os setores, principalmente em relação ao repasse de informações e mudanças de procedimentos. Isso facilitaria o trabalho das equipes e evitaria desencontros de informações.  Também considero importante avaliar melhorias na lanchonete, tanto em relação à variedade e qualidade dos produtos oferecidos quanto aos preços e às opções disponíveis.</t>
+  </si>
+  <si>
+    <t>os preços da lanchonete, que pela manhã é um e tarde é outro, dependendo de quem atende, não tem preço fixo.</t>
+  </si>
+  <si>
+    <t>Espaço de relaxamento para funcionarios. (Ex: academia)</t>
+  </si>
+  <si>
+    <t>Por favor, reintegrar as máquinas de café, disponibilizar alcool para uso na secretaria, verificar sistema de resfriamento do bebedouro da secretaria (devido oscilação de temperatura) da se melhorar a fiscalização da validade dos produtos comercializados na lanchonete.</t>
+  </si>
+  <si>
+    <t>Implantação de segurança interna na Unidade - Banheiro para os colaboradores do CIA - Os serviços da lanchonete deixam a desejar com comida salgada, o mesmo produto com preços diferentes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">É notório a má vigilância quanto ao prazo de validade dos produtos da lanchonete, uma vez que comprei produtos vencidos 4 vezes durante este ano. Uma colega colaboradora teve a má sorte de comprar um salgado com ovos de varingeira junto ao recheio, sem contar com os relatos das demais colegas. Questionamos muito esse ano quanto aos preços dos produtos, o mesmo lanche variando e valor de acordo com o atendente, passando insegurança com a falta de organização da  lanchonete, lanches congelados por dentro, ao todo má qualidade dos alimentos. Com a quebra da máquina de café da secretária, sugiro uma nova para que os colaboradores de todos os setores próximos consigam usufruir. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melhorias nas duas unidades e informações compartilhadas. </t>
+  </si>
+  <si>
+    <t>Em relação à lanchonete, acredito que seja importante reforçar os cuidados com a validade, conservação e qualidade dos alimentos oferecidos. Já tivemos uma situação bastante preocupante em que uma colaboradora encontrou uma varejeira (larva de mosca) dentro de um salgado que estava consumindo. Situações como essa podem representar riscos à saúde e, por isso, seria importante intensificar a fiscalização e os cuidados com o armazenamento e a manipulação dos alimentos.  Quanto à cafeteira da secretaria, estamos sentindo bastante a falta dela, pois era um item que fazia parte da rotina e contribuía para o bem-estar dos colaboradores.</t>
   </si>
 </sst>
 </file>
@@ -266,10 +305,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -337,8 +378,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:R42" totalsRowShown="0">
-  <autoFilter ref="A1:R42" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:R57" totalsRowShown="0">
+  <autoFilter ref="A1:R57" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="18">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="15">
       <extLst>
@@ -470,7 +511,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="rt8JIBHfx0mATf2o1c2YZSr5bAZAsa1Hi1pL7TTHnqJUODZHUjNKOElGSE80SEwyMlBDUE1GN0dPMS4u" isFormConnected="1" maxResponseId="41" latestEventMarker="13">
+      <xlmsforms:msForm id="rt8JIBHfx0mATf2o1c2YZSr5bAZAsa1Hi1pL7TTHnqJUODZHUjNKOElGSE80SEwyMlBDUE1GN0dPMS4u" isFormConnected="1" maxResponseId="56" latestEventMarker="28">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -792,7 +833,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R42"/>
+  <dimension ref="A1:R57"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="18" width="20" bestFit="1" customWidth="1"/>
@@ -3027,6 +3068,816 @@
         <v>64</v>
       </c>
     </row>
+    <row r="43" spans="1:18">
+      <c r="A43" s="3">
+        <v>42</v>
+      </c>
+      <c r="B43" s="2">
+        <v>46295.435717592598</v>
+      </c>
+      <c r="C43" s="2">
+        <v>46295.4375462963</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I43" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J43" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K43" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L43" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M43" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="N43" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="O43" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="P43" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q43" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="R43" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18">
+      <c r="A44" s="3">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2">
+        <v>46295.437349537002</v>
+      </c>
+      <c r="C44" s="2">
+        <v>46295.4384027778</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I44" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J44" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="K44" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="L44" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M44" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="N44" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="O44" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="P44" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q44" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="R44" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18">
+      <c r="A45" s="3">
+        <v>44</v>
+      </c>
+      <c r="B45" s="2">
+        <v>46295.5558564815</v>
+      </c>
+      <c r="C45" s="2">
+        <v>46295.558553240699</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I45" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J45" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K45" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="L45" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="M45" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="N45" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="O45" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="P45" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q45" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="R45" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18">
+      <c r="A46" s="3">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2">
+        <v>46295.581828703696</v>
+      </c>
+      <c r="C46" s="2">
+        <v>46295.583090277803</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I46" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J46" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K46" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="L46" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="M46" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="N46" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="O46" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="P46" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q46" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="R46" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18">
+      <c r="A47" s="3">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2">
+        <v>46295.646840277797</v>
+      </c>
+      <c r="C47" s="2">
+        <v>46295.647743055597</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E47" s="4"/>
+      <c r="F47" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I47" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J47" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K47" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L47" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M47" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="N47" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="O47" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="P47" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q47" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="R47" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18">
+      <c r="A48" s="3">
+        <v>47</v>
+      </c>
+      <c r="B48" s="2">
+        <v>46295.6467708333</v>
+      </c>
+      <c r="C48" s="2">
+        <v>46295.6489814815</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I48" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J48" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="K48" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="L48" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="M48" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="N48" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="O48" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="P48" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q48" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="R48" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18">
+      <c r="A49" s="3">
+        <v>48</v>
+      </c>
+      <c r="B49" s="2">
+        <v>46295.6472222222</v>
+      </c>
+      <c r="C49" s="2">
+        <v>46295.649432870399</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E49" s="4"/>
+      <c r="F49" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I49" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J49" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K49" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L49" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M49" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="N49" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="O49" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="P49" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q49" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="R49" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18">
+      <c r="A50" s="3">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2">
+        <v>46295.647118055596</v>
+      </c>
+      <c r="C50" s="2">
+        <v>46295.652986111098</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E50" s="4"/>
+      <c r="F50" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I50" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J50" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K50" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="L50" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M50" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="N50" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="O50" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="P50" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q50" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="R50" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18">
+      <c r="A51" s="3">
+        <v>50</v>
+      </c>
+      <c r="B51" s="2">
+        <v>46295.647430555597</v>
+      </c>
+      <c r="C51" s="2">
+        <v>46295.654756944401</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E51" s="4"/>
+      <c r="F51" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H51" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I51" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J51" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K51" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L51" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M51" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="N51" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="O51" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="P51" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q51" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="R51" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18">
+      <c r="A52" s="3">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2">
+        <v>46295.649814814802</v>
+      </c>
+      <c r="C52" s="2">
+        <v>46295.657083333303</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E52" s="4"/>
+      <c r="F52" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G52" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H52" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I52" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J52" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="K52" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L52" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M52" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="N52" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="O52" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="P52" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q52" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="R52" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18">
+      <c r="A53" s="3">
+        <v>52</v>
+      </c>
+      <c r="B53" s="2">
+        <v>46295.654861111099</v>
+      </c>
+      <c r="C53" s="2">
+        <v>46295.657268518502</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E53" s="4"/>
+      <c r="F53" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G53" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I53" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J53" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K53" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L53" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M53" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="N53" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="O53" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="P53" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q53" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="R53" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18">
+      <c r="A54" s="3">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2">
+        <v>46295.650081018503</v>
+      </c>
+      <c r="C54" s="2">
+        <v>46295.661134259302</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E54" s="4"/>
+      <c r="F54" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G54" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H54" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I54" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J54" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="K54" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="L54" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="M54" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="N54" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="O54" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="P54" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q54" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="R54" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18">
+      <c r="A55" s="3">
+        <v>54</v>
+      </c>
+      <c r="B55" s="2">
+        <v>46295.6471296296</v>
+      </c>
+      <c r="C55" s="2">
+        <v>46295.661759259303</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E55" s="4"/>
+      <c r="F55" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G55" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H55" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I55" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J55" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="K55" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="L55" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M55" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="N55" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="O55" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="P55" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q55" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="R55" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18">
+      <c r="A56" s="3">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2">
+        <v>46295.657627314802</v>
+      </c>
+      <c r="C56" s="2">
+        <v>46295.662974537001</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E56" s="4"/>
+      <c r="F56" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G56" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H56" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I56" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J56" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K56" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L56" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M56" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="N56" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="O56" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="P56" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q56" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="R56" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18">
+      <c r="A57" s="3">
+        <v>56</v>
+      </c>
+      <c r="B57" s="2">
+        <v>46295.665648148097</v>
+      </c>
+      <c r="C57" s="2">
+        <v>46295.6667592593</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E57" s="4"/>
+      <c r="F57" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G57" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H57" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I57" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J57" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K57" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L57" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M57" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="N57" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="O57" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="P57" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q57" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="R57" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/dados/administrativos.xlsx
+++ b/dados/administrativos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{416327C5-A3DF-40C7-AA74-71B3A97775A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{060FF942-7FDB-4963-90B9-E77981641EF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="802" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="844" uniqueCount="81">
   <si>
     <t>Id</t>
   </si>
@@ -270,6 +270,15 @@
   </si>
   <si>
     <t>Em relação à lanchonete, acredito que seja importante reforçar os cuidados com a validade, conservação e qualidade dos alimentos oferecidos. Já tivemos uma situação bastante preocupante em que uma colaboradora encontrou uma varejeira (larva de mosca) dentro de um salgado que estava consumindo. Situações como essa podem representar riscos à saúde e, por isso, seria importante intensificar a fiscalização e os cuidados com o armazenamento e a manipulação dos alimentos.  Quanto à cafeteira da secretaria, estamos sentindo bastante a falta dela, pois era um item que fazia parte da rotina e contribuía para o bem-estar dos colaboradores.</t>
+  </si>
+  <si>
+    <t>Instrumento de trabalho.</t>
+  </si>
+  <si>
+    <t>sigo satisfeita com a infraestrutura e atendimento.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Poderia colocar um preço fixo no cartão de alimentação. Pôr mês </t>
   </si>
 </sst>
 </file>
@@ -309,8 +318,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -378,8 +387,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:R57" totalsRowShown="0">
-  <autoFilter ref="A1:R57" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:R60" totalsRowShown="0">
+  <autoFilter ref="A1:R60" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="18">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="15">
       <extLst>
@@ -511,7 +520,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="rt8JIBHfx0mATf2o1c2YZSr5bAZAsa1Hi1pL7TTHnqJUODZHUjNKOElGSE80SEwyMlBDUE1GN0dPMS4u" isFormConnected="1" maxResponseId="56" latestEventMarker="28">
+      <xlmsforms:msForm id="rt8JIBHfx0mATf2o1c2YZSr5bAZAsa1Hi1pL7TTHnqJUODZHUjNKOElGSE80SEwyMlBDUE1GN0dPMS4u" isFormConnected="1" maxResponseId="59" latestEventMarker="31">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -833,7 +842,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R57"/>
+  <dimension ref="A1:R60"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="18" width="20" bestFit="1" customWidth="1"/>
@@ -3069,7 +3078,7 @@
       </c>
     </row>
     <row r="43" spans="1:18">
-      <c r="A43" s="3">
+      <c r="A43">
         <v>42</v>
       </c>
       <c r="B43" s="2">
@@ -3078,52 +3087,52 @@
       <c r="C43" s="2">
         <v>46295.4375462963</v>
       </c>
-      <c r="D43" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E43" s="4"/>
-      <c r="F43" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G43" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H43" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I43" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J43" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="K43" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="L43" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="M43" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="N43" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="O43" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="P43" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q43" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="R43" s="4" t="s">
+      <c r="D43" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N43" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O43" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P43" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q43" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R43" s="3" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="44" spans="1:18">
-      <c r="A44" s="3">
+      <c r="A44">
         <v>43</v>
       </c>
       <c r="B44" s="2">
@@ -3132,52 +3141,52 @@
       <c r="C44" s="2">
         <v>46295.4384027778</v>
       </c>
-      <c r="D44" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E44" s="4"/>
-      <c r="F44" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G44" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H44" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I44" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J44" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K44" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="L44" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="M44" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="N44" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="O44" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="P44" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q44" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="R44" s="4" t="s">
+      <c r="D44" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N44" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O44" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q44" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R44" s="3" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="45" spans="1:18">
-      <c r="A45" s="3">
+      <c r="A45">
         <v>44</v>
       </c>
       <c r="B45" s="2">
@@ -3186,52 +3195,52 @@
       <c r="C45" s="2">
         <v>46295.558553240699</v>
       </c>
-      <c r="D45" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E45" s="4"/>
-      <c r="F45" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G45" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H45" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="I45" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="J45" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="K45" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="L45" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="M45" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="N45" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="O45" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="P45" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q45" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="R45" s="4" t="s">
+      <c r="D45" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M45" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N45" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O45" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q45" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="R45" s="3" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="46" spans="1:18">
-      <c r="A46" s="3">
+      <c r="A46">
         <v>45</v>
       </c>
       <c r="B46" s="2">
@@ -3240,52 +3249,52 @@
       <c r="C46" s="2">
         <v>46295.583090277803</v>
       </c>
-      <c r="D46" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E46" s="4"/>
-      <c r="F46" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G46" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H46" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I46" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J46" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K46" s="4" t="s">
+      <c r="D46" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K46" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="L46" s="4" t="s">
+      <c r="L46" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M46" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="N46" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="O46" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="P46" s="4" t="s">
+      <c r="M46" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N46" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O46" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P46" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="Q46" s="4" t="s">
+      <c r="Q46" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="R46" s="4" t="s">
+      <c r="R46" s="3" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="47" spans="1:18">
-      <c r="A47" s="3">
+      <c r="A47">
         <v>46</v>
       </c>
       <c r="B47" s="2">
@@ -3294,52 +3303,52 @@
       <c r="C47" s="2">
         <v>46295.647743055597</v>
       </c>
-      <c r="D47" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E47" s="4"/>
-      <c r="F47" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G47" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H47" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I47" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J47" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="K47" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L47" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="M47" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="N47" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="O47" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="P47" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q47" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="R47" s="4" t="s">
+      <c r="D47" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E47" s="3"/>
+      <c r="F47" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K47" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M47" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q47" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R47" s="3" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="48" spans="1:18">
-      <c r="A48" s="3">
+      <c r="A48">
         <v>47</v>
       </c>
       <c r="B48" s="2">
@@ -3348,52 +3357,52 @@
       <c r="C48" s="2">
         <v>46295.6489814815</v>
       </c>
-      <c r="D48" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E48" s="4"/>
-      <c r="F48" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G48" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H48" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I48" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J48" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K48" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="L48" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="M48" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="N48" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="O48" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="P48" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q48" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="R48" s="4" t="s">
+      <c r="D48" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E48" s="3"/>
+      <c r="F48" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L48" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M48" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N48" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O48" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P48" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q48" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R48" s="3" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="49" spans="1:18">
-      <c r="A49" s="3">
+      <c r="A49">
         <v>48</v>
       </c>
       <c r="B49" s="2">
@@ -3402,52 +3411,52 @@
       <c r="C49" s="2">
         <v>46295.649432870399</v>
       </c>
-      <c r="D49" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E49" s="4"/>
-      <c r="F49" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G49" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H49" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I49" s="4" t="s">
+      <c r="D49" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E49" s="3"/>
+      <c r="F49" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I49" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="J49" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="K49" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L49" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="M49" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="N49" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="O49" s="4" t="s">
+      <c r="J49" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K49" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L49" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M49" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N49" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O49" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="P49" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q49" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="R49" s="4" t="s">
+      <c r="P49" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q49" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R49" s="3" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="50" spans="1:18">
-      <c r="A50" s="3">
+      <c r="A50">
         <v>49</v>
       </c>
       <c r="B50" s="2">
@@ -3456,52 +3465,52 @@
       <c r="C50" s="2">
         <v>46295.652986111098</v>
       </c>
-      <c r="D50" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E50" s="4"/>
-      <c r="F50" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G50" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H50" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I50" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J50" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="K50" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="L50" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="M50" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="N50" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="O50" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="P50" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q50" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="R50" s="4" t="s">
+      <c r="D50" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L50" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M50" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N50" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O50" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P50" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q50" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R50" s="3" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="51" spans="1:18">
-      <c r="A51" s="3">
+      <c r="A51">
         <v>50</v>
       </c>
       <c r="B51" s="2">
@@ -3510,52 +3519,52 @@
       <c r="C51" s="2">
         <v>46295.654756944401</v>
       </c>
-      <c r="D51" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E51" s="4"/>
-      <c r="F51" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G51" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H51" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I51" s="4" t="s">
+      <c r="D51" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E51" s="3"/>
+      <c r="F51" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I51" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="J51" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="K51" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L51" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="M51" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="N51" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="O51" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="P51" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q51" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="R51" s="4" t="s">
+      <c r="J51" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K51" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L51" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M51" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N51" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O51" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P51" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q51" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R51" s="3" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="52" spans="1:18">
-      <c r="A52" s="3">
+      <c r="A52">
         <v>51</v>
       </c>
       <c r="B52" s="2">
@@ -3564,52 +3573,52 @@
       <c r="C52" s="2">
         <v>46295.657083333303</v>
       </c>
-      <c r="D52" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E52" s="4"/>
-      <c r="F52" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G52" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H52" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I52" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J52" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K52" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L52" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="M52" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="N52" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="O52" s="4" t="s">
+      <c r="D52" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E52" s="3"/>
+      <c r="F52" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M52" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N52" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O52" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="P52" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q52" s="4" t="s">
+      <c r="P52" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q52" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="R52" s="4" t="s">
+      <c r="R52" s="3" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="53" spans="1:18">
-      <c r="A53" s="3">
+      <c r="A53">
         <v>52</v>
       </c>
       <c r="B53" s="2">
@@ -3618,52 +3627,52 @@
       <c r="C53" s="2">
         <v>46295.657268518502</v>
       </c>
-      <c r="D53" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E53" s="4"/>
-      <c r="F53" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G53" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H53" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I53" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J53" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K53" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L53" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="M53" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="N53" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="O53" s="4" t="s">
+      <c r="D53" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E53" s="3"/>
+      <c r="F53" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I53" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J53" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K53" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L53" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M53" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N53" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O53" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="P53" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q53" s="4" t="s">
+      <c r="P53" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q53" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="R53" s="4" t="s">
+      <c r="R53" s="3" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="54" spans="1:18">
-      <c r="A54" s="3">
+      <c r="A54">
         <v>53</v>
       </c>
       <c r="B54" s="2">
@@ -3672,52 +3681,52 @@
       <c r="C54" s="2">
         <v>46295.661134259302</v>
       </c>
-      <c r="D54" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E54" s="4"/>
-      <c r="F54" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G54" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H54" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="I54" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J54" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K54" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="L54" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="M54" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="N54" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="O54" s="4" t="s">
+      <c r="D54" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E54" s="3"/>
+      <c r="F54" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K54" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L54" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M54" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N54" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O54" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="P54" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q54" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="R54" s="4" t="s">
+      <c r="P54" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q54" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R54" s="3" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="55" spans="1:18">
-      <c r="A55" s="3">
+      <c r="A55">
         <v>54</v>
       </c>
       <c r="B55" s="2">
@@ -3726,52 +3735,52 @@
       <c r="C55" s="2">
         <v>46295.661759259303</v>
       </c>
-      <c r="D55" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E55" s="4"/>
-      <c r="F55" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G55" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H55" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I55" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J55" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K55" s="4" t="s">
+      <c r="D55" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E55" s="3"/>
+      <c r="F55" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I55" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J55" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K55" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="L55" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="M55" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="N55" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="O55" s="4" t="s">
+      <c r="L55" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M55" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N55" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O55" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="P55" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q55" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="R55" s="4" t="s">
+      <c r="P55" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q55" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R55" s="3" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="56" spans="1:18">
-      <c r="A56" s="3">
+      <c r="A56">
         <v>55</v>
       </c>
       <c r="B56" s="2">
@@ -3780,52 +3789,52 @@
       <c r="C56" s="2">
         <v>46295.662974537001</v>
       </c>
-      <c r="D56" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E56" s="4"/>
-      <c r="F56" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G56" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H56" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I56" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J56" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K56" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L56" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="M56" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="N56" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="O56" s="4" t="s">
+      <c r="D56" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E56" s="3"/>
+      <c r="F56" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I56" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J56" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K56" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L56" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M56" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N56" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O56" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="P56" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q56" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="R56" s="4" t="s">
+      <c r="P56" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q56" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R56" s="3" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="57" spans="1:18">
-      <c r="A57" s="3">
+      <c r="A57">
         <v>56</v>
       </c>
       <c r="B57" s="2">
@@ -3834,48 +3843,210 @@
       <c r="C57" s="2">
         <v>46295.6667592593</v>
       </c>
-      <c r="D57" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E57" s="4"/>
-      <c r="F57" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G57" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H57" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I57" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J57" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K57" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L57" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="M57" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="N57" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="O57" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="P57" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q57" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="R57" s="4" t="s">
+      <c r="D57" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E57" s="3"/>
+      <c r="F57" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K57" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L57" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M57" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N57" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O57" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P57" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q57" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R57" s="3" t="s">
         <v>25</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18">
+      <c r="A58" s="4">
+        <v>57</v>
+      </c>
+      <c r="B58" s="2">
+        <v>46296.4374074074</v>
+      </c>
+      <c r="C58" s="2">
+        <v>46296.439826388902</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E58" s="3"/>
+      <c r="F58" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K58" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L58" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M58" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N58" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O58" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P58" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q58" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R58" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18">
+      <c r="A59" s="4">
+        <v>58</v>
+      </c>
+      <c r="B59" s="2">
+        <v>46296.650740740697</v>
+      </c>
+      <c r="C59" s="2">
+        <v>46296.655069444401</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E59" s="3"/>
+      <c r="F59" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K59" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="L59" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="M59" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N59" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="O59" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P59" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q59" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="R59" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18">
+      <c r="A60" s="4">
+        <v>59</v>
+      </c>
+      <c r="B60" s="2">
+        <v>46296.669282407398</v>
+      </c>
+      <c r="C60" s="2">
+        <v>46296.671550925901</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E60" s="3"/>
+      <c r="F60" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K60" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L60" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M60" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N60" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O60" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P60" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q60" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R60" s="3" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/dados/administrativos.xlsx
+++ b/dados/administrativos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30601"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{060FF942-7FDB-4963-90B9-E77981641EF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9540901D-0962-4D4E-855F-C067FE9D4C30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="844" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="82">
   <si>
     <t>Id</t>
   </si>
@@ -279,6 +279,9 @@
   </si>
   <si>
     <t xml:space="preserve">Poderia colocar um preço fixo no cartão de alimentação. Pôr mês </t>
+  </si>
+  <si>
+    <t>Ambientes bem organizados.</t>
   </si>
 </sst>
 </file>
@@ -314,12 +317,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -387,8 +389,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:R60" totalsRowShown="0">
-  <autoFilter ref="A1:R60" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:R61" totalsRowShown="0">
+  <autoFilter ref="A1:R61" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="18">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="15">
       <extLst>
@@ -520,7 +522,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="rt8JIBHfx0mATf2o1c2YZSr5bAZAsa1Hi1pL7TTHnqJUODZHUjNKOElGSE80SEwyMlBDUE1GN0dPMS4u" isFormConnected="1" maxResponseId="59" latestEventMarker="31">
+      <xlmsforms:msForm id="rt8JIBHfx0mATf2o1c2YZSr5bAZAsa1Hi1pL7TTHnqJUODZHUjNKOElGSE80SEwyMlBDUE1GN0dPMS4u" isFormConnected="1" maxResponseId="60" latestEventMarker="32">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -842,7 +844,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R60"/>
+  <dimension ref="A1:R61"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="18" width="20" bestFit="1" customWidth="1"/>
@@ -3888,7 +3890,7 @@
       </c>
     </row>
     <row r="58" spans="1:18">
-      <c r="A58" s="4">
+      <c r="A58">
         <v>57</v>
       </c>
       <c r="B58" s="2">
@@ -3942,7 +3944,7 @@
       </c>
     </row>
     <row r="59" spans="1:18">
-      <c r="A59" s="4">
+      <c r="A59">
         <v>58</v>
       </c>
       <c r="B59" s="2">
@@ -3996,7 +3998,7 @@
       </c>
     </row>
     <row r="60" spans="1:18">
-      <c r="A60" s="4">
+      <c r="A60">
         <v>59</v>
       </c>
       <c r="B60" s="2">
@@ -4047,6 +4049,60 @@
       </c>
       <c r="R60" s="3" t="s">
         <v>80</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" s="2">
+        <v>46296.696342592601</v>
+      </c>
+      <c r="C61" s="2">
+        <v>46296.700312499997</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E61" s="3"/>
+      <c r="F61" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I61" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J61" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K61" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L61" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M61" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N61" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O61" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P61" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q61" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R61" s="3" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>

--- a/dados/administrativos.xlsx
+++ b/dados/administrativos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30602"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9540901D-0962-4D4E-855F-C067FE9D4C30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6D0DB3A1-0AAB-4469-B6D7-548254BE9A65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="85">
   <si>
     <t>Id</t>
   </si>
@@ -282,6 +282,15 @@
   </si>
   <si>
     <t>Ambientes bem organizados.</t>
+  </si>
+  <si>
+    <t>A lanchonete deveria melhorar, pois não há muita variedade no cardápio. Seria interessante oferecer mais opções de lanches e pratos para atender melhor aos clientes.</t>
+  </si>
+  <si>
+    <t>De modo geral, considero que a instituição apresenta uma boa estrutura para o desenvolvimento das atividades administrativas, especialmente em relação aos espaços de atendimento, ambiente de trabalho, áreas de descanso e convivência, infraestrutura tecnológica e acessibilidade.  Entretanto, acredito que existem alguns pontos que precisam de maior atenção e aprimoramento. Destaco principalmente a necessidade de fortalecer a valorização e o desenvolvimento dos profissionais. Muitas vezes, os colaboradores são incentivados a realizar diversos cursos e capacitações, inclusive como forma de preparação para oportunidades de crescimento dentro da própria instituição. Porém, quando surge uma vaga interna, são exigidos diversos requisitos e cursos para que o funcionário possa concorrer, mesmo quando candidatos externos não possuem a mesma trajetória de capacitação e experiência dentro da instituição. Em algumas situações, após todo esse investimento de tempo e dedicação, o colaborador acaba não sendo aproveitado e a vaga é preenchida por alguém de fora.  Acredito que os profissionais que já fazem parte da instituição, conhecem seus processos, sua cultura e demonstram interesse em se desenvolver deveriam ter suas qualificações e experiências internas consideradas de forma mais efetiva nos processos seletivos. Valorizar o crescimento profissional interno também pode contribuir para a motivação, o comprometimento e a permanência dos colaboradores.  Além disso, considero importante ampliar a transparência e a participação dos colaboradores na gestão institucional e melhorar a comunicação interna, garantindo que as informações sejam repassadas de forma clara, ágil e alinhada entre os setores.  Também considero importante investir na melhoria da limpeza e conservação dos espaços, bem como reforçar as medidas de segurança, tanto dentro quanto no entorno das unidades. Esses aspectos contribuem diretamente para proporcionar um ambiente de trabalho mais adequado, seguro e acolhedor para colaboradores e acadêmicos.  De forma geral, reconheço os aspectos positivos da estrutura existente, mas acredito que melhorias nesses pontos contribuiriam significativamente para a valorização dos profissionais, a qualidade do ambiente institucional e a satisfação dos colaboradores.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melhora lá na lanchonete </t>
   </si>
 </sst>
 </file>
@@ -317,11 +326,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -389,8 +399,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:R61" totalsRowShown="0">
-  <autoFilter ref="A1:R61" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:R64" totalsRowShown="0">
+  <autoFilter ref="A1:R64" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="18">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="15">
       <extLst>
@@ -522,7 +532,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="rt8JIBHfx0mATf2o1c2YZSr5bAZAsa1Hi1pL7TTHnqJUODZHUjNKOElGSE80SEwyMlBDUE1GN0dPMS4u" isFormConnected="1" maxResponseId="60" latestEventMarker="32">
+      <xlmsforms:msForm id="rt8JIBHfx0mATf2o1c2YZSr5bAZAsa1Hi1pL7TTHnqJUODZHUjNKOElGSE80SEwyMlBDUE1GN0dPMS4u" isFormConnected="1" maxResponseId="63" latestEventMarker="35">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -844,7 +854,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R61"/>
+  <dimension ref="A1:R64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="18" width="20" bestFit="1" customWidth="1"/>
@@ -4105,6 +4115,168 @@
         <v>81</v>
       </c>
     </row>
+    <row r="62" spans="1:18">
+      <c r="A62" s="4">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2">
+        <v>46301.403356481504</v>
+      </c>
+      <c r="C62" s="2">
+        <v>46301.406446759298</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E62" s="3"/>
+      <c r="F62" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K62" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M62" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N62" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O62" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="P62" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q62" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="R62" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18">
+      <c r="A63" s="4">
+        <v>62</v>
+      </c>
+      <c r="B63" s="2">
+        <v>46301.399386574099</v>
+      </c>
+      <c r="C63" s="2">
+        <v>46301.408645833297</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E63" s="3"/>
+      <c r="F63" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I63" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J63" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K63" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L63" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M63" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N63" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O63" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P63" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q63" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="R63" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18">
+      <c r="A64" s="4">
+        <v>63</v>
+      </c>
+      <c r="B64" s="2">
+        <v>46301.503263888902</v>
+      </c>
+      <c r="C64" s="2">
+        <v>46301.508587962999</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E64" s="3"/>
+      <c r="F64" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J64" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K64" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L64" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M64" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N64" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O64" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P64" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q64" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="R64" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/dados/administrativos.xlsx
+++ b/dados/administrativos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6D0DB3A1-0AAB-4469-B6D7-548254BE9A65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{85D59BDC-F6C7-4CF0-B7DB-328BF145DDF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="956" uniqueCount="89">
   <si>
     <t>Id</t>
   </si>
@@ -291,6 +291,18 @@
   </si>
   <si>
     <t xml:space="preserve">Melhora lá na lanchonete </t>
+  </si>
+  <si>
+    <t>Parabéns por sempre buscar melhorar!</t>
+  </si>
+  <si>
+    <t>Melhorar a questão dos terceirizados no quesito lanchonete. Preços exagerados e qualidade de certo modo deixa a desejar</t>
+  </si>
+  <si>
+    <t>Dá oportunidades de mudança de cargo para os colaboradores, principalmente os da limpeza que nunca tem oportunidades. Pessoas do administrativo as vezes trocam mais de uma vez de função.</t>
+  </si>
+  <si>
+    <t>De modo geral, minha percepção inicial da instituição é bastante positiva. Estou conhecendo a dinâmica institucional e os processos de trabalho, mas até o momento tenho me sentido bem acolhida e satisfeita com o ambiente. Espero continuar aprendendo, contribuindo com a equipe e acompanhando o desenvolvimento da instituição.</t>
   </si>
 </sst>
 </file>
@@ -399,8 +411,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:R64" totalsRowShown="0">
-  <autoFilter ref="A1:R64" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:R68" totalsRowShown="0">
+  <autoFilter ref="A1:R68" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="18">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="15">
       <extLst>
@@ -532,7 +544,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="rt8JIBHfx0mATf2o1c2YZSr5bAZAsa1Hi1pL7TTHnqJUODZHUjNKOElGSE80SEwyMlBDUE1GN0dPMS4u" isFormConnected="1" maxResponseId="63" latestEventMarker="35">
+      <xlmsforms:msForm id="rt8JIBHfx0mATf2o1c2YZSr5bAZAsa1Hi1pL7TTHnqJUODZHUjNKOElGSE80SEwyMlBDUE1GN0dPMS4u" isFormConnected="1" maxResponseId="67" latestEventMarker="39">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -854,7 +866,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R64"/>
+  <dimension ref="A1:R68"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="18" width="20" bestFit="1" customWidth="1"/>
@@ -4116,7 +4128,7 @@
       </c>
     </row>
     <row r="62" spans="1:18">
-      <c r="A62" s="4">
+      <c r="A62">
         <v>61</v>
       </c>
       <c r="B62" s="2">
@@ -4170,7 +4182,7 @@
       </c>
     </row>
     <row r="63" spans="1:18">
-      <c r="A63" s="4">
+      <c r="A63">
         <v>62</v>
       </c>
       <c r="B63" s="2">
@@ -4224,7 +4236,7 @@
       </c>
     </row>
     <row r="64" spans="1:18">
-      <c r="A64" s="4">
+      <c r="A64">
         <v>63</v>
       </c>
       <c r="B64" s="2">
@@ -4275,6 +4287,222 @@
       </c>
       <c r="R64" s="3" t="s">
         <v>84</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18">
+      <c r="A65" s="4">
+        <v>64</v>
+      </c>
+      <c r="B65" s="2">
+        <v>46301.664085648197</v>
+      </c>
+      <c r="C65" s="2">
+        <v>46301.668611111098</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E65" s="3"/>
+      <c r="F65" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I65" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J65" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K65" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L65" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M65" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N65" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O65" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P65" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q65" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R65" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18">
+      <c r="A66" s="4">
+        <v>65</v>
+      </c>
+      <c r="B66" s="2">
+        <v>46301.698796296303</v>
+      </c>
+      <c r="C66" s="2">
+        <v>46301.702696759297</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E66" s="3"/>
+      <c r="F66" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K66" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L66" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M66" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N66" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O66" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="P66" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q66" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R66" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="67" spans="1:18">
+      <c r="A67" s="4">
+        <v>66</v>
+      </c>
+      <c r="B67" s="2">
+        <v>46302.427326388897</v>
+      </c>
+      <c r="C67" s="2">
+        <v>46302.429120370398</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E67" s="3"/>
+      <c r="F67" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I67" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J67" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K67" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L67" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M67" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N67" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O67" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P67" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q67" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R67" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="68" spans="1:18">
+      <c r="A68" s="4">
+        <v>67</v>
+      </c>
+      <c r="B68" s="2">
+        <v>46302.4366435185</v>
+      </c>
+      <c r="C68" s="2">
+        <v>46302.439178240696</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E68" s="3"/>
+      <c r="F68" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I68" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J68" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K68" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L68" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M68" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N68" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O68" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="P68" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q68" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="R68" s="3" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/dados/administrativos.xlsx
+++ b/dados/administrativos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{85D59BDC-F6C7-4CF0-B7DB-328BF145DDF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E44E275C-5736-4CD0-BB38-7D6E4CF4594E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="956" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1264" uniqueCount="105">
   <si>
     <t>Id</t>
   </si>
@@ -303,6 +303,54 @@
   </si>
   <si>
     <t>De modo geral, minha percepção inicial da instituição é bastante positiva. Estou conhecendo a dinâmica institucional e os processos de trabalho, mas até o momento tenho me sentido bem acolhida e satisfeita com o ambiente. Espero continuar aprendendo, contribuindo com a equipe e acompanhando o desenvolvimento da instituição.</t>
+  </si>
+  <si>
+    <t>Sugiro que a lanchonete melhore na qualidade dos produtos</t>
+  </si>
+  <si>
+    <t>Sempre há espaço para melhoria. Em uma instituição com a infraestrutura completa e extensa, cada detalhe importa e é importante o zelo dela, seja acadêmico ou não.</t>
+  </si>
+  <si>
+    <t>O serviço prestado pelas lanchonetes das unidades deixa a desejar. É comum serem oferecidos alimentos requentados e frituras com aspecto e sabor que sugerem a reutilização excessiva do óleo. Além disso, os preços dos produtos não são apresentados de forma clara ao consumidor, o que gera a percepção de que os valores são definidos de maneira pouco padronizada e por conveniência.</t>
+  </si>
+  <si>
+    <t>Tudo muito bom!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iluminação na passarela que leva ao bloco II, pois a noite fica muito escuro. A lanchonete precisa padronizar os preços e deixá-los a mostra. Necessário uma cobertura do CIA ligada a passarela, pois em períodos de chuva fica descoberto impossibilitando saída dos funcionários e a entrada dos estudantes. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melhorar a segurando dentro da faculdade </t>
+  </si>
+  <si>
+    <t>Sem sugestões.</t>
+  </si>
+  <si>
+    <t>Entrei recentemente e até o momento a minha experiência aqui na Catolica está sendo muito boooa! Obrigada</t>
+  </si>
+  <si>
+    <t>Em relação a valorização dos profissionais, ao surgirem vagas com melhores salários, quase nunca é um funcionário antigo que ocupa a vaga, a preferência acaba sendo de pessoas de fora, assim os funcionários de casa permanecem com salários inferiores, sem contar que existe setor que não tem distinção de funções, são todos auxiliares, enquanto em outros possui assistente, e analista, o que possibilita que mesmo que o funcionário não mude de setor ao surgir uma vaga dentro do mesmo setor ele poderia subir de nível, o que não ocorre por exemplo no CIA, onde todos são auxiliares. Ainda em relação a valorização, recebemos a Norma do Programa de Prêmio por Desempenho  Comercial, nela informa que há a bonificação para 3.15. Reabertura: estudante com matrícula inativa — trancada ou cancelada — que solicita retomada no mesmo curso, condicionada à ausência superior a dois semestres  letivos consecutivos. Aplicável exclusivamente ao Ensino Superior. 3.16. Reabertura com Transferência Interna: estudante com matrícula inativa que solicita retomada em curso diferente do anterior, dentro da mesma instituição,  observada a mesma condicionante temporal de ausência superior a dois semestres  letivos consecutivos. Aplicável exclusivamente ao Ensino Superior - Estes atendimentos são realizados em nossa unidade pelo CIA, e a execução no sistema pela equipe da Secretaria, no entanto não há bonificação para estes setores que realmente atua no atendimento ao aluno que está retornando aos estudos. em relação a lanchonete, os preços são altos, sugiro que possa existir uma tabela de preços ou menu, pois os preços são altos e variam de acordo com quem está atendendo, um tabelamento evitaria surpresa de aumento sem prévio aviso ou a depender de quem está atendendo no momento.</t>
+  </si>
+  <si>
+    <t>Muito proveitosa as perguntas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melhorias e aperfeiçoamento, para estarmos em constante avanço. </t>
+  </si>
+  <si>
+    <t>segurança externa pode melhorar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Os valores da cantina não condiz com a qualidade. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estou satisfeita </t>
+  </si>
+  <si>
+    <t>Não tenho.</t>
   </si>
 </sst>
 </file>
@@ -411,8 +459,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:R68" totalsRowShown="0">
-  <autoFilter ref="A1:R68" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:R90" totalsRowShown="0">
+  <autoFilter ref="A1:R90" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="18">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="15">
       <extLst>
@@ -544,7 +592,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="rt8JIBHfx0mATf2o1c2YZSr5bAZAsa1Hi1pL7TTHnqJUODZHUjNKOElGSE80SEwyMlBDUE1GN0dPMS4u" isFormConnected="1" maxResponseId="67" latestEventMarker="39">
+      <xlmsforms:msForm id="rt8JIBHfx0mATf2o1c2YZSr5bAZAsa1Hi1pL7TTHnqJUODZHUjNKOElGSE80SEwyMlBDUE1GN0dPMS4u" isFormConnected="1" maxResponseId="89" latestEventMarker="61">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -866,7 +914,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R68"/>
+  <dimension ref="A1:R90"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="18" width="20" bestFit="1" customWidth="1"/>
@@ -4290,7 +4338,7 @@
       </c>
     </row>
     <row r="65" spans="1:18">
-      <c r="A65" s="4">
+      <c r="A65">
         <v>64</v>
       </c>
       <c r="B65" s="2">
@@ -4344,7 +4392,7 @@
       </c>
     </row>
     <row r="66" spans="1:18">
-      <c r="A66" s="4">
+      <c r="A66">
         <v>65</v>
       </c>
       <c r="B66" s="2">
@@ -4398,7 +4446,7 @@
       </c>
     </row>
     <row r="67" spans="1:18">
-      <c r="A67" s="4">
+      <c r="A67">
         <v>66</v>
       </c>
       <c r="B67" s="2">
@@ -4452,7 +4500,7 @@
       </c>
     </row>
     <row r="68" spans="1:18">
-      <c r="A68" s="4">
+      <c r="A68">
         <v>67</v>
       </c>
       <c r="B68" s="2">
@@ -4503,6 +4551,1194 @@
       </c>
       <c r="R68" s="3" t="s">
         <v>88</v>
+      </c>
+    </row>
+    <row r="69" spans="1:18">
+      <c r="A69" s="4">
+        <v>68</v>
+      </c>
+      <c r="B69" s="2">
+        <v>46303.394618055601</v>
+      </c>
+      <c r="C69" s="2">
+        <v>46303.395243055602</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E69" s="3"/>
+      <c r="F69" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I69" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J69" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K69" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L69" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M69" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N69" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O69" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P69" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q69" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R69" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="70" spans="1:18">
+      <c r="A70" s="4">
+        <v>69</v>
+      </c>
+      <c r="B70" s="2">
+        <v>46303.395706018498</v>
+      </c>
+      <c r="C70" s="2">
+        <v>46303.396701388898</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E70" s="3"/>
+      <c r="F70" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I70" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J70" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K70" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L70" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M70" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N70" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="O70" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P70" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q70" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R70" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="71" spans="1:18">
+      <c r="A71" s="4">
+        <v>70</v>
+      </c>
+      <c r="B71" s="2">
+        <v>46303.404340277797</v>
+      </c>
+      <c r="C71" s="2">
+        <v>46303.406620370399</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E71" s="3"/>
+      <c r="F71" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I71" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J71" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K71" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L71" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M71" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N71" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O71" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P71" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q71" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="R71" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="72" spans="1:18">
+      <c r="A72" s="4">
+        <v>71</v>
+      </c>
+      <c r="B72" s="2">
+        <v>46303.405208333301</v>
+      </c>
+      <c r="C72" s="2">
+        <v>46303.408437500002</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E72" s="3"/>
+      <c r="F72" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K72" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L72" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M72" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N72" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O72" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P72" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q72" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R72" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="73" spans="1:18">
+      <c r="A73" s="4">
+        <v>72</v>
+      </c>
+      <c r="B73" s="2">
+        <v>46303.415509259299</v>
+      </c>
+      <c r="C73" s="2">
+        <v>46303.415879629603</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E73" s="3"/>
+      <c r="F73" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I73" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J73" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K73" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L73" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M73" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N73" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O73" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="P73" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q73" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="R73" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="74" spans="1:18">
+      <c r="A74" s="4">
+        <v>73</v>
+      </c>
+      <c r="B74" s="2">
+        <v>46303.450439814798</v>
+      </c>
+      <c r="C74" s="2">
+        <v>46303.4527662037</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E74" s="3"/>
+      <c r="F74" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I74" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J74" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K74" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L74" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M74" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N74" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O74" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P74" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q74" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="R74" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18">
+      <c r="A75" s="4">
+        <v>74</v>
+      </c>
+      <c r="B75" s="2">
+        <v>46303.4523611111</v>
+      </c>
+      <c r="C75" s="2">
+        <v>46303.453055555598</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E75" s="3"/>
+      <c r="F75" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I75" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J75" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K75" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L75" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M75" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N75" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O75" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P75" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q75" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R75" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18">
+      <c r="A76" s="4">
+        <v>75</v>
+      </c>
+      <c r="B76" s="2">
+        <v>46303.452233796299</v>
+      </c>
+      <c r="C76" s="2">
+        <v>46303.453645833302</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E76" s="3"/>
+      <c r="F76" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K76" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L76" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M76" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N76" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O76" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="P76" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q76" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R76" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="77" spans="1:18">
+      <c r="A77" s="4">
+        <v>76</v>
+      </c>
+      <c r="B77" s="2">
+        <v>46303.4692013889</v>
+      </c>
+      <c r="C77" s="2">
+        <v>46303.469745370399</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E77" s="3"/>
+      <c r="F77" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I77" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J77" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K77" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L77" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M77" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N77" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O77" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="P77" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q77" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R77" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="78" spans="1:18">
+      <c r="A78" s="4">
+        <v>77</v>
+      </c>
+      <c r="B78" s="2">
+        <v>46303.518333333297</v>
+      </c>
+      <c r="C78" s="2">
+        <v>46303.519201388903</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E78" s="3"/>
+      <c r="F78" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I78" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J78" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K78" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L78" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M78" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N78" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O78" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P78" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q78" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R78" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="79" spans="1:18">
+      <c r="A79" s="4">
+        <v>78</v>
+      </c>
+      <c r="B79" s="2">
+        <v>46303.520115740699</v>
+      </c>
+      <c r="C79" s="2">
+        <v>46303.520914351902</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E79" s="3"/>
+      <c r="F79" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I79" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J79" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K79" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L79" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M79" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N79" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O79" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P79" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q79" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R79" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="80" spans="1:18">
+      <c r="A80" s="4">
+        <v>79</v>
+      </c>
+      <c r="B80" s="2">
+        <v>46303.521585648203</v>
+      </c>
+      <c r="C80" s="2">
+        <v>46303.522372685198</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E80" s="3"/>
+      <c r="F80" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I80" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J80" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K80" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L80" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M80" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N80" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O80" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P80" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q80" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R80" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="81" spans="1:18">
+      <c r="A81" s="4">
+        <v>80</v>
+      </c>
+      <c r="B81" s="2">
+        <v>46303.576736111099</v>
+      </c>
+      <c r="C81" s="2">
+        <v>46303.579236111102</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E81" s="3"/>
+      <c r="F81" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K81" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L81" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M81" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N81" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O81" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="P81" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q81" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="R81" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="82" spans="1:18">
+      <c r="A82" s="4">
+        <v>81</v>
+      </c>
+      <c r="B82" s="2">
+        <v>46303.573252314804</v>
+      </c>
+      <c r="C82" s="2">
+        <v>46303.589212963001</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E82" s="3"/>
+      <c r="F82" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I82" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J82" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K82" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L82" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M82" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N82" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O82" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P82" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q82" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R82" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="83" spans="1:18">
+      <c r="A83" s="4">
+        <v>82</v>
+      </c>
+      <c r="B83" s="2">
+        <v>46303.600358796299</v>
+      </c>
+      <c r="C83" s="2">
+        <v>46303.601006944402</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E83" s="3"/>
+      <c r="F83" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L83" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M83" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N83" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O83" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P83" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q83" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="R83" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="84" spans="1:18">
+      <c r="A84" s="4">
+        <v>83</v>
+      </c>
+      <c r="B84" s="2">
+        <v>46303.600497685198</v>
+      </c>
+      <c r="C84" s="2">
+        <v>46303.601585648197</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E84" s="3"/>
+      <c r="F84" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I84" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J84" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K84" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L84" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M84" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N84" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="O84" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P84" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q84" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R84" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="85" spans="1:18">
+      <c r="A85" s="4">
+        <v>84</v>
+      </c>
+      <c r="B85" s="2">
+        <v>46303.599976851903</v>
+      </c>
+      <c r="C85" s="2">
+        <v>46303.602557870399</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E85" s="3"/>
+      <c r="F85" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H85" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I85" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J85" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K85" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L85" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M85" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N85" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O85" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P85" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q85" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R85" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="86" spans="1:18">
+      <c r="A86" s="4">
+        <v>85</v>
+      </c>
+      <c r="B86" s="2">
+        <v>46303.624710648102</v>
+      </c>
+      <c r="C86" s="2">
+        <v>46303.625983796301</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E86" s="3"/>
+      <c r="F86" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H86" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I86" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J86" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K86" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L86" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M86" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N86" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O86" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P86" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q86" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R86" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="87" spans="1:18">
+      <c r="A87" s="4">
+        <v>86</v>
+      </c>
+      <c r="B87" s="2">
+        <v>46303.688865740703</v>
+      </c>
+      <c r="C87" s="2">
+        <v>46303.690625000003</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E87" s="3"/>
+      <c r="F87" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H87" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I87" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J87" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K87" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L87" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M87" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N87" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O87" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P87" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q87" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R87" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="88" spans="1:18">
+      <c r="A88" s="4">
+        <v>87</v>
+      </c>
+      <c r="B88" s="2">
+        <v>46304.438599537003</v>
+      </c>
+      <c r="C88" s="2">
+        <v>46304.440706018497</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E88" s="3"/>
+      <c r="F88" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H88" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I88" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J88" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K88" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L88" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M88" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N88" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O88" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P88" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q88" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R88" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="89" spans="1:18">
+      <c r="A89" s="4">
+        <v>88</v>
+      </c>
+      <c r="B89" s="2">
+        <v>46304.465949074103</v>
+      </c>
+      <c r="C89" s="2">
+        <v>46304.469236111101</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E89" s="3"/>
+      <c r="F89" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K89" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L89" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M89" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N89" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O89" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P89" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q89" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R89" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="90" spans="1:18">
+      <c r="A90" s="4">
+        <v>89</v>
+      </c>
+      <c r="B90" s="2">
+        <v>46304.467835648102</v>
+      </c>
+      <c r="C90" s="2">
+        <v>46304.469409722202</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E90" s="3"/>
+      <c r="F90" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G90" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H90" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I90" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J90" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K90" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L90" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M90" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N90" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O90" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P90" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q90" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R90" s="3" t="s">
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/dados/administrativos.xlsx
+++ b/dados/administrativos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30602"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30606"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E44E275C-5736-4CD0-BB38-7D6E4CF4594E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2CA14ED5-CDC0-48DB-8541-F65E85D03250}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -386,12 +386,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4554,7 +4553,7 @@
       </c>
     </row>
     <row r="69" spans="1:18">
-      <c r="A69" s="4">
+      <c r="A69">
         <v>68</v>
       </c>
       <c r="B69" s="2">
@@ -4608,7 +4607,7 @@
       </c>
     </row>
     <row r="70" spans="1:18">
-      <c r="A70" s="4">
+      <c r="A70">
         <v>69</v>
       </c>
       <c r="B70" s="2">
@@ -4662,7 +4661,7 @@
       </c>
     </row>
     <row r="71" spans="1:18">
-      <c r="A71" s="4">
+      <c r="A71">
         <v>70</v>
       </c>
       <c r="B71" s="2">
@@ -4716,7 +4715,7 @@
       </c>
     </row>
     <row r="72" spans="1:18">
-      <c r="A72" s="4">
+      <c r="A72">
         <v>71</v>
       </c>
       <c r="B72" s="2">
@@ -4770,7 +4769,7 @@
       </c>
     </row>
     <row r="73" spans="1:18">
-      <c r="A73" s="4">
+      <c r="A73">
         <v>72</v>
       </c>
       <c r="B73" s="2">
@@ -4824,7 +4823,7 @@
       </c>
     </row>
     <row r="74" spans="1:18">
-      <c r="A74" s="4">
+      <c r="A74">
         <v>73</v>
       </c>
       <c r="B74" s="2">
@@ -4878,7 +4877,7 @@
       </c>
     </row>
     <row r="75" spans="1:18">
-      <c r="A75" s="4">
+      <c r="A75">
         <v>74</v>
       </c>
       <c r="B75" s="2">
@@ -4932,7 +4931,7 @@
       </c>
     </row>
     <row r="76" spans="1:18">
-      <c r="A76" s="4">
+      <c r="A76">
         <v>75</v>
       </c>
       <c r="B76" s="2">
@@ -4986,7 +4985,7 @@
       </c>
     </row>
     <row r="77" spans="1:18">
-      <c r="A77" s="4">
+      <c r="A77">
         <v>76</v>
       </c>
       <c r="B77" s="2">
@@ -5040,7 +5039,7 @@
       </c>
     </row>
     <row r="78" spans="1:18">
-      <c r="A78" s="4">
+      <c r="A78">
         <v>77</v>
       </c>
       <c r="B78" s="2">
@@ -5094,7 +5093,7 @@
       </c>
     </row>
     <row r="79" spans="1:18">
-      <c r="A79" s="4">
+      <c r="A79">
         <v>78</v>
       </c>
       <c r="B79" s="2">
@@ -5148,7 +5147,7 @@
       </c>
     </row>
     <row r="80" spans="1:18">
-      <c r="A80" s="4">
+      <c r="A80">
         <v>79</v>
       </c>
       <c r="B80" s="2">
@@ -5202,7 +5201,7 @@
       </c>
     </row>
     <row r="81" spans="1:18">
-      <c r="A81" s="4">
+      <c r="A81">
         <v>80</v>
       </c>
       <c r="B81" s="2">
@@ -5256,7 +5255,7 @@
       </c>
     </row>
     <row r="82" spans="1:18">
-      <c r="A82" s="4">
+      <c r="A82">
         <v>81</v>
       </c>
       <c r="B82" s="2">
@@ -5310,7 +5309,7 @@
       </c>
     </row>
     <row r="83" spans="1:18">
-      <c r="A83" s="4">
+      <c r="A83">
         <v>82</v>
       </c>
       <c r="B83" s="2">
@@ -5364,7 +5363,7 @@
       </c>
     </row>
     <row r="84" spans="1:18">
-      <c r="A84" s="4">
+      <c r="A84">
         <v>83</v>
       </c>
       <c r="B84" s="2">
@@ -5418,7 +5417,7 @@
       </c>
     </row>
     <row r="85" spans="1:18">
-      <c r="A85" s="4">
+      <c r="A85">
         <v>84</v>
       </c>
       <c r="B85" s="2">
@@ -5472,7 +5471,7 @@
       </c>
     </row>
     <row r="86" spans="1:18">
-      <c r="A86" s="4">
+      <c r="A86">
         <v>85</v>
       </c>
       <c r="B86" s="2">
@@ -5526,7 +5525,7 @@
       </c>
     </row>
     <row r="87" spans="1:18">
-      <c r="A87" s="4">
+      <c r="A87">
         <v>86</v>
       </c>
       <c r="B87" s="2">
@@ -5580,7 +5579,7 @@
       </c>
     </row>
     <row r="88" spans="1:18">
-      <c r="A88" s="4">
+      <c r="A88">
         <v>87</v>
       </c>
       <c r="B88" s="2">
@@ -5634,7 +5633,7 @@
       </c>
     </row>
     <row r="89" spans="1:18">
-      <c r="A89" s="4">
+      <c r="A89">
         <v>88</v>
       </c>
       <c r="B89" s="2">
@@ -5688,7 +5687,7 @@
       </c>
     </row>
     <row r="90" spans="1:18">
-      <c r="A90" s="4">
+      <c r="A90">
         <v>89</v>
       </c>
       <c r="B90" s="2">

--- a/dados/administrativos.xlsx
+++ b/dados/administrativos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30606"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30610"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2CA14ED5-CDC0-48DB-8541-F65E85D03250}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{51A06A2E-7407-42B3-B162-EEE02D80F539}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1264" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1306" uniqueCount="108">
   <si>
     <t>Id</t>
   </si>
@@ -351,6 +351,15 @@
   </si>
   <si>
     <t>Não tenho.</t>
+  </si>
+  <si>
+    <t>Nd</t>
+  </si>
+  <si>
+    <t>Sem sugestão de melhoria momentaneamente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUGESTÃO:TER UM TÉCNICO DE CAMPO NO SERVIÇO AGROPECUÁRIA PARA ATUAR NO DIA A DIA DA EQUIPE DE CAMPO ,PARA ORGANIZAR AS TAREFAS E AS DEMANDAS DOS PROFESSORES E TAMBÉM E O MANEJO DOS ANIMAIS </t>
   </si>
 </sst>
 </file>
@@ -386,11 +395,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -458,8 +468,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:R90" totalsRowShown="0">
-  <autoFilter ref="A1:R90" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:R93" totalsRowShown="0">
+  <autoFilter ref="A1:R93" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="18">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="15">
       <extLst>
@@ -591,7 +601,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="rt8JIBHfx0mATf2o1c2YZSr5bAZAsa1Hi1pL7TTHnqJUODZHUjNKOElGSE80SEwyMlBDUE1GN0dPMS4u" isFormConnected="1" maxResponseId="89" latestEventMarker="61">
+      <xlmsforms:msForm id="rt8JIBHfx0mATf2o1c2YZSr5bAZAsa1Hi1pL7TTHnqJUODZHUjNKOElGSE80SEwyMlBDUE1GN0dPMS4u" isFormConnected="1" maxResponseId="92" latestEventMarker="64">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -913,7 +923,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R90"/>
+  <dimension ref="A1:R93"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="18" width="20" bestFit="1" customWidth="1"/>
@@ -5740,6 +5750,168 @@
         <v>104</v>
       </c>
     </row>
+    <row r="91" spans="1:18">
+      <c r="A91" s="4">
+        <v>90</v>
+      </c>
+      <c r="B91" s="2">
+        <v>46308.506724537001</v>
+      </c>
+      <c r="C91" s="2">
+        <v>46308.507800925901</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E91" s="3"/>
+      <c r="F91" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K91" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L91" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M91" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N91" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="O91" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P91" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q91" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R91" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="92" spans="1:18">
+      <c r="A92" s="4">
+        <v>91</v>
+      </c>
+      <c r="B92" s="2">
+        <v>46308.687199074098</v>
+      </c>
+      <c r="C92" s="2">
+        <v>46308.692280092597</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E92" s="3"/>
+      <c r="F92" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G92" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H92" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I92" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J92" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K92" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L92" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M92" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N92" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O92" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P92" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q92" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R92" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="93" spans="1:18">
+      <c r="A93" s="4">
+        <v>92</v>
+      </c>
+      <c r="B93" s="2">
+        <v>46311.283715277801</v>
+      </c>
+      <c r="C93" s="2">
+        <v>46311.287314814799</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E93" s="3"/>
+      <c r="F93" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G93" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H93" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I93" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J93" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K93" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L93" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M93" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N93" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O93" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P93" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q93" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R93" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/dados/administrativos.xlsx
+++ b/dados/administrativos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{51A06A2E-7407-42B3-B162-EEE02D80F539}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A0A34D4F-B8A8-4B0C-91D4-7BCC5659C14D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -395,12 +395,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5751,7 +5750,7 @@
       </c>
     </row>
     <row r="91" spans="1:18">
-      <c r="A91" s="4">
+      <c r="A91">
         <v>90</v>
       </c>
       <c r="B91" s="2">
@@ -5805,7 +5804,7 @@
       </c>
     </row>
     <row r="92" spans="1:18">
-      <c r="A92" s="4">
+      <c r="A92">
         <v>91</v>
       </c>
       <c r="B92" s="2">
@@ -5859,7 +5858,7 @@
       </c>
     </row>
     <row r="93" spans="1:18">
-      <c r="A93" s="4">
+      <c r="A93">
         <v>92</v>
       </c>
       <c r="B93" s="2">
